--- a/static/master_excel_solution.xlsx
+++ b/static/master_excel_solution.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" windowWidth="28800" windowHeight="12300" firstSheet="1" activeTab="1"/>
+    <workbookView showHorizontalScroll="0" windowWidth="28800" windowHeight="12300" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="7" state="hidden" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="311">
   <si>
     <t>Name</t>
   </si>
@@ -583,13 +583,208 @@
     <t>Name &amp; Parish</t>
   </si>
   <si>
-    <t>Stbotolph Aldersgate</t>
-  </si>
-  <si>
-    <t>Stclementdanes</t>
-  </si>
-  <si>
-    <t>Stdunstan In The West</t>
+    <t xml:space="preserve"> &amp; Sutton, Surrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Great St Helen, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Andrew Holborn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Wapping, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Horne, Surrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Hornsoy, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Godmersham, Kent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Heath, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Aldermanbury, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Martin In The Fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Eastwood, Essex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Bradwell Jaxta Mare, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Ham Charleton Kings, Gloucester</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stbotolph Aldersgate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Lawrence, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Lomster Horeford</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Martin In The Fields, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Keire Worcester</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Giles In The Fields, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Clement Danes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Blackdon Devon</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Anne Westminster</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St George Botolph Lane, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Boddington, Surrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stoake Northampton</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Sepulchre, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Ampthill, Beds</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Lambeth, Surrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Sepulchre</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Swithin, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stafford</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stclementdanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Chelsea, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Boreham, Essex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Gadsden, Herts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stenning Sussex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Dunstan In The West</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Feversham Said County</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Windsor Berks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stdunstan In The West</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Stanton, Wilts</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; East Grimstead Sussex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Canterbury</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Deale</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Bride, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Edmundthe King Lombard Street, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Giles Cripplegate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Westminster</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Finchamstead Berks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Alford Lincoln</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Waltham Abbey, Essex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Islington, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Peter Le Poor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St James Clerkenwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Charlwood, Surrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Rusper Sussex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Sittingbourne, Kent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Alban Wood Street, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Ickingham, Middlesex</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Mary Whitechapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Maiden Lane, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Catherine Coleman, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Islington</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; St Botolph Billingsgate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Nicholas Lane, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Corby Kesteven Lincoln, London</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Henley On Thames</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> &amp; Croydon, Surrey</t>
   </si>
   <si>
     <t>Calculate the Sum, Average, Maximum, and Minimum values of column A in cells B3, C3, D3, and E3 respectively.</t>
@@ -628,19 +823,19 @@
     <t>30</t>
   </si>
   <si>
+    <t>Joseph</t>
+  </si>
+  <si>
     <t>25</t>
   </si>
   <si>
-    <t>Joseph</t>
-  </si>
-  <si>
     <t>45</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>Trim the text in column A, place the trimmed results in column B, and calculate their lengths in column C.</t>
+    <t>Trim the text in column A, place the trimmed results in column B, and calculate Column B lengths in column C.</t>
   </si>
   <si>
     <t>Trim</t>
@@ -2567,15 +2762,15 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>184</v>
+        <v>249</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>243</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:2">
@@ -3008,7 +3203,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:1">
@@ -3053,7 +3248,7 @@
     </row>
     <row r="10" ht="15" spans="1:1">
       <c r="A10" s="3" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" ht="15" spans="1:1">
@@ -5350,10 +5545,10 @@
         <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="C3" s="3" t="str">
-        <f>CONCATENATE(A3," &amp; ",B3)</f>
+        <f t="shared" ref="C3:C66" si="0">CONCATENATE(A3,B3)</f>
         <v>Edward &amp; Sutton, Surrey</v>
       </c>
     </row>
@@ -5362,10 +5557,10 @@
         <v>109</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="C4" s="3" t="str">
-        <f t="shared" ref="C4:C35" si="0">CONCATENATE(A4," &amp; ",B4)</f>
+        <f t="shared" si="0"/>
         <v>Bobert &amp; Great St Helen, London</v>
       </c>
     </row>
@@ -5374,7 +5569,7 @@
         <v>137</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="C5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5386,7 +5581,7 @@
         <v>160</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>28</v>
+        <v>183</v>
       </c>
       <c r="C6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5398,7 +5593,7 @@
         <v>95</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>184</v>
       </c>
       <c r="C7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5410,7 +5605,7 @@
         <v>120</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="C8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5422,7 +5617,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>186</v>
       </c>
       <c r="C9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5434,7 +5629,7 @@
         <v>132</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5446,7 +5641,7 @@
         <v>102</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="C11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5458,7 +5653,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5470,7 +5665,7 @@
         <v>141</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="C13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5482,7 +5677,7 @@
         <v>100</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="C14" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5494,7 +5689,7 @@
         <v>101</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="C15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5506,7 +5701,7 @@
         <v>105</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="C16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5518,7 +5713,7 @@
         <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>194</v>
       </c>
       <c r="C17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5530,7 +5725,7 @@
         <v>108</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>195</v>
       </c>
       <c r="C18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5542,7 +5737,7 @@
         <v>110</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>196</v>
       </c>
       <c r="C19" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5554,7 +5749,7 @@
         <v>118</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>197</v>
       </c>
       <c r="C20" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5566,7 +5761,7 @@
         <v>119</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="C21" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5578,7 +5773,7 @@
         <v>135</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5590,7 +5785,7 @@
         <v>136</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="C23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5602,7 +5797,7 @@
         <v>140</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c r="C24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5614,7 +5809,7 @@
         <v>18</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>46</v>
+        <v>201</v>
       </c>
       <c r="C25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5626,7 +5821,7 @@
         <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>47</v>
+        <v>202</v>
       </c>
       <c r="C26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5638,7 +5833,7 @@
         <v>144</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>48</v>
+        <v>203</v>
       </c>
       <c r="C27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5650,7 +5845,7 @@
         <v>12</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>49</v>
+        <v>204</v>
       </c>
       <c r="C28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5662,7 +5857,7 @@
         <v>97</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>50</v>
+        <v>205</v>
       </c>
       <c r="C29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5674,7 +5869,7 @@
         <v>98</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="C30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5686,7 +5881,7 @@
         <v>99</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="C31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5698,7 +5893,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="C32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5710,7 +5905,7 @@
         <v>104</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>54</v>
+        <v>209</v>
       </c>
       <c r="C33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5722,7 +5917,7 @@
         <v>106</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>55</v>
+        <v>210</v>
       </c>
       <c r="C34" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5734,7 +5929,7 @@
         <v>16</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5746,10 +5941,10 @@
         <v>17</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>57</v>
+        <v>212</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f t="shared" ref="C36:C81" si="1">CONCATENATE(A36," &amp; ",B36)</f>
+        <f t="shared" si="0"/>
         <v>Blase &amp; Chelsea, Middlesex</v>
       </c>
     </row>
@@ -5758,10 +5953,10 @@
         <v>111</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>58</v>
+        <v>213</v>
       </c>
       <c r="C37" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Cornelius &amp; Boreham, Essex</v>
       </c>
     </row>
@@ -5770,10 +5965,10 @@
         <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>59</v>
+        <v>214</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Cresswell &amp; Gadsden, Herts</v>
       </c>
     </row>
@@ -5782,10 +5977,10 @@
         <v>15</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="C39" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Cressy &amp; Stenning Sussex</v>
       </c>
     </row>
@@ -5794,10 +5989,10 @@
         <v>113</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="C40" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Creswell &amp; St Dunstan In The West</v>
       </c>
     </row>
@@ -5806,10 +6001,10 @@
         <v>114</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>62</v>
+        <v>217</v>
       </c>
       <c r="C41" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Crofts &amp; Feversham Said County</v>
       </c>
     </row>
@@ -5818,10 +6013,10 @@
         <v>115</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Curwen &amp; Windsor Berks</v>
       </c>
     </row>
@@ -5830,10 +6025,10 @@
         <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Cuthbert &amp; Stdunstan In The West</v>
       </c>
     </row>
@@ -5842,10 +6037,10 @@
         <v>121</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Dennis &amp; Stanton, Wilts</v>
       </c>
     </row>
@@ -5854,10 +6049,10 @@
         <v>122</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Dionisious &amp; East Grimstead Sussex</v>
       </c>
     </row>
@@ -5866,10 +6061,10 @@
         <v>123</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>67</v>
+        <v>222</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Dionysius &amp; Canterbury</v>
       </c>
     </row>
@@ -5878,10 +6073,10 @@
         <v>125</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>68</v>
+        <v>223</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Edwin &amp; Deale</v>
       </c>
     </row>
@@ -5890,10 +6085,10 @@
         <v>126</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="C48" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Eliceum &amp; St Bride, London</v>
       </c>
     </row>
@@ -5902,10 +6097,10 @@
         <v>127</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Elkanah &amp; St Sepulchre</v>
       </c>
     </row>
@@ -5914,10 +6109,10 @@
         <v>128</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Ellionem &amp; St Bride, London</v>
       </c>
     </row>
@@ -5926,10 +6121,10 @@
         <v>129</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Frame &amp; St Martin In The Fields</v>
       </c>
     </row>
@@ -5938,10 +6133,10 @@
         <v>130</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>70</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Gabriel &amp; St Edmundthe King Lombard Street, London</v>
       </c>
     </row>
@@ -5950,10 +6145,10 @@
         <v>131</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>71</v>
+        <v>226</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Hamnett &amp; St Giles Cripplegate</v>
       </c>
     </row>
@@ -5962,10 +6157,10 @@
         <v>133</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>72</v>
+        <v>227</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>James &amp; Westminster</v>
       </c>
     </row>
@@ -5974,10 +6169,10 @@
         <v>138</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>73</v>
+        <v>228</v>
       </c>
       <c r="C55" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Lambarte &amp; Finchamstead Berks</v>
       </c>
     </row>
@@ -5986,10 +6181,10 @@
         <v>145</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="C56" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Paramor &amp; St Andrew Holborn</v>
       </c>
     </row>
@@ -5998,10 +6193,10 @@
         <v>146</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>74</v>
+        <v>229</v>
       </c>
       <c r="C57" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Paslowe &amp; Alford Lincoln</v>
       </c>
     </row>
@@ -6010,10 +6205,10 @@
         <v>147</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Petit &amp; Waltham Abbey, Essex</v>
       </c>
     </row>
@@ -6022,10 +6217,10 @@
         <v>148</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Phanuel &amp; Islington, Middlesex</v>
       </c>
     </row>
@@ -6034,10 +6229,10 @@
         <v>149</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="C60" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Rae &amp; Windsor Berks</v>
       </c>
     </row>
@@ -6046,10 +6241,10 @@
         <v>150</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="C61" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Randol &amp; St Peter Le Poor</v>
       </c>
     </row>
@@ -6058,10 +6253,10 @@
         <v>151</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C62" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Ratsey &amp; St Martin In The Fields</v>
       </c>
     </row>
@@ -6070,10 +6265,10 @@
         <v>152</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>78</v>
+        <v>233</v>
       </c>
       <c r="C63" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sadeskewe &amp; St James Clerkenwell</v>
       </c>
     </row>
@@ -6082,10 +6277,10 @@
         <v>153</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="C64" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Saile &amp; Charlwood, Surrey</v>
       </c>
     </row>
@@ -6094,10 +6289,10 @@
         <v>154</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>61</v>
+        <v>216</v>
       </c>
       <c r="C65" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Sheapheard &amp; St Dunstan In The West</v>
       </c>
     </row>
@@ -6106,10 +6301,10 @@
         <v>155</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C66" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Stanyan &amp; St Martin In The Fields</v>
       </c>
     </row>
@@ -6118,10 +6313,10 @@
         <v>156</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="C67" s="3" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="C67:C81" si="1">CONCATENATE(A67,B67)</f>
         <v>Swynborne &amp; Lambeth, Surrey</v>
       </c>
     </row>
@@ -6130,7 +6325,7 @@
         <v>157</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="C68" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6142,7 +6337,7 @@
         <v>158</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="C69" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6154,7 +6349,7 @@
         <v>159</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>82</v>
+        <v>237</v>
       </c>
       <c r="C70" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6166,7 +6361,7 @@
         <v>161</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="C71" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6178,7 +6373,7 @@
         <v>8</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>83</v>
+        <v>238</v>
       </c>
       <c r="C72" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6190,7 +6385,7 @@
         <v>11</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="C73" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6202,7 +6397,7 @@
         <v>117</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="C74" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6214,7 +6409,7 @@
         <v>94</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>86</v>
+        <v>241</v>
       </c>
       <c r="C75" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6226,7 +6421,7 @@
         <v>5</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="C76" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6238,7 +6433,7 @@
         <v>103</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>88</v>
+        <v>243</v>
       </c>
       <c r="C77" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6250,7 +6445,7 @@
         <v>142</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>89</v>
+        <v>244</v>
       </c>
       <c r="C78" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6262,7 +6457,7 @@
         <v>139</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>90</v>
+        <v>245</v>
       </c>
       <c r="C79" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6274,7 +6469,7 @@
         <v>134</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>91</v>
+        <v>246</v>
       </c>
       <c r="C80" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6286,7 +6481,7 @@
         <v>96</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>92</v>
+        <v>247</v>
       </c>
       <c r="C81" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6312,24 +6507,24 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" ht="15" spans="1:5">
       <c r="A2" s="11" t="s">
-        <v>184</v>
+        <v>249</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>186</v>
+        <v>251</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>188</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" ht="15" spans="1:5">
@@ -7075,7 +7270,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7083,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>163</v>
@@ -7094,7 +7289,7 @@
         <v>95</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>167</v>
@@ -7105,7 +7300,7 @@
         <v>102</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>192</v>
+        <v>257</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>168</v>
@@ -7116,7 +7311,7 @@
         <v>109</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>165</v>
@@ -7127,7 +7322,7 @@
         <v>120</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>167</v>
@@ -7138,7 +7333,7 @@
         <v>124</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>164</v>
@@ -7149,7 +7344,7 @@
         <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>167</v>
@@ -7157,24 +7352,24 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>195</v>
+        <v>260</v>
+      </c>
+      <c r="B9" s="6">
+        <v>26</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B10" s="6">
-        <v>26</v>
+        <v>132</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7182,7 +7377,7 @@
         <v>137</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>165</v>
@@ -7193,7 +7388,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>168</v>
@@ -7204,7 +7399,7 @@
         <v>160</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>166</v>
@@ -7233,7 +7428,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -7241,15 +7436,15 @@
         <v>21</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="B3" s="8" t="str">
         <f>TRIM(A3)</f>
@@ -7262,7 +7457,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="B4" s="8" t="str">
         <f t="shared" ref="B4:B35" si="0">TRIM(A4)</f>
@@ -7275,7 +7470,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="B5" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7288,7 +7483,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="B6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7301,7 +7496,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="B7" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7314,7 +7509,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>207</v>
+        <v>272</v>
       </c>
       <c r="B8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7327,7 +7522,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>273</v>
       </c>
       <c r="B9" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7340,7 +7535,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="B10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7353,7 +7548,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>210</v>
+        <v>275</v>
       </c>
       <c r="B11" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7379,7 +7574,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="B13" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7392,7 +7587,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="B14" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7405,7 +7600,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
-        <v>213</v>
+        <v>278</v>
       </c>
       <c r="B15" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7431,7 +7626,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
-        <v>214</v>
+        <v>279</v>
       </c>
       <c r="B17" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7457,7 +7652,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="B19" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7483,7 +7678,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
-        <v>216</v>
+        <v>281</v>
       </c>
       <c r="B21" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7548,7 +7743,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>217</v>
+        <v>282</v>
       </c>
       <c r="B26" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7561,7 +7756,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
-        <v>218</v>
+        <v>283</v>
       </c>
       <c r="B27" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7587,7 +7782,7 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>219</v>
+        <v>284</v>
       </c>
       <c r="B29" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7600,7 +7795,7 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="3" t="s">
-        <v>220</v>
+        <v>285</v>
       </c>
       <c r="B30" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7613,7 +7808,7 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
-        <v>221</v>
+        <v>286</v>
       </c>
       <c r="B31" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7639,7 +7834,7 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="3" t="s">
-        <v>222</v>
+        <v>287</v>
       </c>
       <c r="B33" s="8" t="str">
         <f t="shared" si="0"/>
@@ -7678,7 +7873,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="3" t="s">
-        <v>223</v>
+        <v>288</v>
       </c>
       <c r="B36" s="8" t="str">
         <f t="shared" ref="B36:B81" si="2">TRIM(A36)</f>
@@ -7691,7 +7886,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="3" t="s">
-        <v>224</v>
+        <v>289</v>
       </c>
       <c r="B37" s="8" t="str">
         <f t="shared" si="2"/>
@@ -7704,7 +7899,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
-        <v>225</v>
+        <v>290</v>
       </c>
       <c r="B38" s="8" t="str">
         <f t="shared" si="2"/>
@@ -7834,7 +8029,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="3" t="s">
-        <v>226</v>
+        <v>291</v>
       </c>
       <c r="B48" s="8" t="str">
         <f t="shared" si="2"/>
@@ -7860,7 +8055,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="3" t="s">
-        <v>226</v>
+        <v>291</v>
       </c>
       <c r="B50" s="8" t="str">
         <f t="shared" si="2"/>
@@ -7886,7 +8081,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="3" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="B52" s="8" t="str">
         <f t="shared" si="2"/>
@@ -7964,7 +8159,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="3" t="s">
-        <v>228</v>
+        <v>293</v>
       </c>
       <c r="B58" s="8" t="str">
         <f t="shared" si="2"/>
@@ -7977,7 +8172,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="3" t="s">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="B59" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8042,7 +8237,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="3" t="s">
-        <v>230</v>
+        <v>295</v>
       </c>
       <c r="B64" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8081,7 +8276,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="3" t="s">
-        <v>221</v>
+        <v>286</v>
       </c>
       <c r="B67" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8107,7 +8302,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="3" t="s">
-        <v>231</v>
+        <v>296</v>
       </c>
       <c r="B69" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8120,7 +8315,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="3" t="s">
-        <v>232</v>
+        <v>297</v>
       </c>
       <c r="B70" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8133,7 +8328,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="3" t="s">
-        <v>229</v>
+        <v>294</v>
       </c>
       <c r="B71" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8146,7 +8341,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="3" t="s">
-        <v>233</v>
+        <v>298</v>
       </c>
       <c r="B72" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8172,7 +8367,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="3" t="s">
-        <v>234</v>
+        <v>299</v>
       </c>
       <c r="B74" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8185,7 +8380,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="3" t="s">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="B75" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8224,7 +8419,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="3" t="s">
-        <v>236</v>
+        <v>301</v>
       </c>
       <c r="B78" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8237,7 +8432,7 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="3" t="s">
-        <v>237</v>
+        <v>302</v>
       </c>
       <c r="B79" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8263,7 +8458,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="3" t="s">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="B81" s="8" t="str">
         <f t="shared" si="2"/>
@@ -8294,7 +8489,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>239</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="1" spans="1:3">
@@ -8302,10 +8497,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>240</v>
+        <v>305</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>241</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="1" spans="1:3">
